--- a/Mataquito/data/sample_metadata/MataquitoSampleData.xlsx
+++ b/Mataquito/data/sample_metadata/MataquitoSampleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/AndesTG/Mataquito/data/sample_metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/data/sample_metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8850F06B-2748-3449-B0EB-36709086CE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1661453-7574-594E-ACBC-E666ADD06E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="21860" xr2:uid="{822C4A32-E1B2-FB43-A333-01FAD55EB50E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21800" xr2:uid="{822C4A32-E1B2-FB43-A333-01FAD55EB50E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>Quartz</t>
   </si>
   <si>
-    <t>07KNSTD3110</t>
-  </si>
-  <si>
     <t>10Be/9Be</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>CT-8</t>
+  </si>
+  <si>
+    <t>9Be carrier (g)</t>
   </si>
 </sst>
 </file>
@@ -563,28 +563,28 @@
         <v>20</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
@@ -981,7 +981,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
